--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129724871</v>
+        <v>129724939</v>
       </c>
       <c r="B2" t="n">
-        <v>79694</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571145</v>
+        <v>571038</v>
       </c>
       <c r="R2" t="n">
-        <v>6467460</v>
+        <v>6467439</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,38 +777,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129724939</v>
+        <v>129724871</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>79695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571038</v>
+        <v>571145</v>
       </c>
       <c r="R3" t="n">
-        <v>6467439</v>
+        <v>6467460</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +881,7 @@
         <v>129724735</v>
       </c>
       <c r="B4" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>129724814</v>
       </c>
       <c r="B5" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129724930</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129724793</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129724723</v>
       </c>
       <c r="B9" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129724784</v>
       </c>
       <c r="B10" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129724754</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>129724740</v>
       </c>
       <c r="B13" t="n">
-        <v>75187</v>
+        <v>75188</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129724806</v>
       </c>
       <c r="B14" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129724939</v>
+        <v>129724871</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>79700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571038</v>
+        <v>571145</v>
       </c>
       <c r="R2" t="n">
-        <v>6467439</v>
+        <v>6467460</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129724871</v>
+        <v>129724939</v>
       </c>
       <c r="B3" t="n">
-        <v>79695</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571145</v>
+        <v>571038</v>
       </c>
       <c r="R3" t="n">
-        <v>6467460</v>
+        <v>6467439</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +881,7 @@
         <v>129724735</v>
       </c>
       <c r="B4" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>129724814</v>
       </c>
       <c r="B5" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129724793</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129724723</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129724784</v>
       </c>
       <c r="B10" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129724754</v>
       </c>
       <c r="B11" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>129724740</v>
       </c>
       <c r="B13" t="n">
-        <v>75188</v>
+        <v>75193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129724806</v>
       </c>
       <c r="B14" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129724871</v>
+        <v>129724939</v>
       </c>
       <c r="B2" t="n">
-        <v>79700</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571145</v>
+        <v>571038</v>
       </c>
       <c r="R2" t="n">
-        <v>6467460</v>
+        <v>6467439</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,38 +777,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129724939</v>
+        <v>129724871</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571038</v>
+        <v>571145</v>
       </c>
       <c r="R3" t="n">
-        <v>6467439</v>
+        <v>6467460</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129724939</v>
+        <v>129724871</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>79700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571038</v>
+        <v>571145</v>
       </c>
       <c r="R2" t="n">
-        <v>6467439</v>
+        <v>6467460</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129724871</v>
+        <v>129724939</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571145</v>
+        <v>571038</v>
       </c>
       <c r="R3" t="n">
-        <v>6467460</v>
+        <v>6467439</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>129724939</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129724735</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>129724814</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129724793</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129724723</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129724784</v>
       </c>
       <c r="B10" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129724754</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129724806</v>
       </c>
       <c r="B14" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129724871</v>
+        <v>129724939</v>
       </c>
       <c r="B2" t="n">
-        <v>79700</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571145</v>
+        <v>571038</v>
       </c>
       <c r="R2" t="n">
-        <v>6467460</v>
+        <v>6467439</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,38 +777,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129724939</v>
+        <v>129724871</v>
       </c>
       <c r="B3" t="n">
-        <v>98778</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571038</v>
+        <v>571145</v>
       </c>
       <c r="R3" t="n">
-        <v>6467439</v>
+        <v>6467460</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +881,7 @@
         <v>129724735</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>129724814</v>
       </c>
       <c r="B5" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129724793</v>
       </c>
       <c r="B7" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129724723</v>
       </c>
       <c r="B9" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129724784</v>
       </c>
       <c r="B10" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129724754</v>
       </c>
       <c r="B11" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129724806</v>
       </c>
       <c r="B14" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129724939</v>
+        <v>129724871</v>
       </c>
       <c r="B2" t="n">
-        <v>98780</v>
+        <v>79700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571038</v>
+        <v>571145</v>
       </c>
       <c r="R2" t="n">
-        <v>6467439</v>
+        <v>6467460</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129724871</v>
+        <v>129724939</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>98780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571145</v>
+        <v>571038</v>
       </c>
       <c r="R3" t="n">
-        <v>6467460</v>
+        <v>6467439</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>129724939</v>
       </c>
       <c r="B3" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129724735</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>129724814</v>
       </c>
       <c r="B5" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129724793</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129724723</v>
       </c>
       <c r="B9" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129724754</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129724871</v>
       </c>
       <c r="B2" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129724939</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129724735</v>
       </c>
       <c r="B4" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>129724814</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129724930</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129724793</v>
       </c>
       <c r="B7" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129724723</v>
       </c>
       <c r="B9" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129724784</v>
       </c>
       <c r="B10" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129724754</v>
       </c>
       <c r="B11" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>129724740</v>
       </c>
       <c r="B13" t="n">
-        <v>75193</v>
+        <v>75196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129724806</v>
       </c>
       <c r="B14" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129724871</v>
+        <v>129724939</v>
       </c>
       <c r="B2" t="n">
-        <v>79703</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571145</v>
+        <v>571038</v>
       </c>
       <c r="R2" t="n">
-        <v>6467460</v>
+        <v>6467439</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,38 +777,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129724939</v>
+        <v>129724871</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>79706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571038</v>
+        <v>571145</v>
       </c>
       <c r="R3" t="n">
-        <v>6467439</v>
+        <v>6467460</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +881,7 @@
         <v>129724735</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>129724814</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129724930</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129724793</v>
       </c>
       <c r="B7" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129724723</v>
       </c>
       <c r="B9" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129724784</v>
       </c>
       <c r="B10" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129724754</v>
       </c>
       <c r="B11" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>129724740</v>
       </c>
       <c r="B13" t="n">
-        <v>75196</v>
+        <v>75199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129724806</v>
       </c>
       <c r="B14" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129724939</v>
+        <v>129724871</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>79707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571038</v>
+        <v>571145</v>
       </c>
       <c r="R2" t="n">
-        <v>6467439</v>
+        <v>6467460</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +776,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129724871</v>
+        <v>129724939</v>
       </c>
       <c r="B3" t="n">
-        <v>79706</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571145</v>
+        <v>571038</v>
       </c>
       <c r="R3" t="n">
-        <v>6467460</v>
+        <v>6467439</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +881,7 @@
         <v>129724735</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>129724814</v>
       </c>
       <c r="B5" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129724793</v>
       </c>
       <c r="B7" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129724723</v>
       </c>
       <c r="B9" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129724784</v>
       </c>
       <c r="B10" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129724754</v>
       </c>
       <c r="B11" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129724806</v>
       </c>
       <c r="B14" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129724871</v>
+        <v>129724939</v>
       </c>
       <c r="B2" t="n">
-        <v>79707</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571145</v>
+        <v>571038</v>
       </c>
       <c r="R2" t="n">
-        <v>6467460</v>
+        <v>6467439</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,38 +777,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129724939</v>
+        <v>129724871</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>79708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571038</v>
+        <v>571145</v>
       </c>
       <c r="R3" t="n">
-        <v>6467439</v>
+        <v>6467460</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +881,7 @@
         <v>129724735</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>129724814</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129724930</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>129724793</v>
       </c>
       <c r="B7" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129724723</v>
       </c>
       <c r="B9" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129724784</v>
       </c>
       <c r="B10" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>129724754</v>
       </c>
       <c r="B11" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>129724740</v>
       </c>
       <c r="B13" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>129724806</v>
       </c>
       <c r="B14" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -2043,7 +2043,7 @@
         <v>131082500</v>
       </c>
       <c r="B15" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -2043,7 +2043,7 @@
         <v>131082500</v>
       </c>
       <c r="B15" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -2043,7 +2043,7 @@
         <v>131082500</v>
       </c>
       <c r="B15" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2156,6 +2156,119 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132469770</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58109</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Parsen, naturskogsrest Holmen Skog, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>571083</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6467308</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -2161,7 +2161,7 @@
         <v>132469770</v>
       </c>
       <c r="B16" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 6146-2025 artfynd.xlsx
+++ b/artfynd/A 6146-2025 artfynd.xlsx
@@ -2161,7 +2161,7 @@
         <v>132469770</v>
       </c>
       <c r="B16" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
